--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.86366946312235</v>
+        <v>5.015346287757382</v>
       </c>
       <c r="D2" t="n">
-        <v>31.05485122191129</v>
+        <v>5.046413323560585</v>
       </c>
       <c r="E2" t="n">
-        <v>3.348714682747866</v>
+        <v>0.5441661359465284</v>
       </c>
       <c r="F2" t="n">
-        <v>3.512904203188445</v>
+        <v>0.5708469330181223</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.16624009762661</v>
+        <v>3.927014015864325</v>
       </c>
       <c r="D3" t="n">
-        <v>24.0290428155344</v>
+        <v>3.90471945752434</v>
       </c>
       <c r="E3" t="n">
-        <v>3.348714682747866</v>
+        <v>0.5441661359465284</v>
       </c>
       <c r="F3" t="n">
-        <v>3.512904203188445</v>
+        <v>0.5708469330181223</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
